--- a/data/df_merged.xlsx
+++ b/data/df_merged.xlsx
@@ -1888,7 +1888,7 @@
         <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
         <v>1</v>
@@ -1959,7 +1959,7 @@
         <v>22</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -2721,7 +2721,7 @@
         <v>33</v>
       </c>
       <c r="C31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
         <v>1</v>
@@ -3027,7 +3027,7 @@
         <v>37</v>
       </c>
       <c r="C35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="n">
         <v>1</v>
@@ -3179,7 +3179,7 @@
         <v>39</v>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37" t="n">
         <v>1</v>
@@ -4093,7 +4093,7 @@
         <v>52</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -4249,7 +4249,7 @@
         <v>54</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -4788,7 +4788,7 @@
         <v>61</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -4936,7 +4936,7 @@
         <v>63</v>
       </c>
       <c r="C60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -5013,7 +5013,7 @@
         <v>64</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -5090,7 +5090,7 @@
         <v>65</v>
       </c>
       <c r="C62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -5167,7 +5167,7 @@
         <v>66</v>
       </c>
       <c r="C63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -6286,7 +6286,7 @@
         <v>81</v>
       </c>
       <c r="C78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D78" t="n">
         <v>0</v>
@@ -6363,7 +6363,7 @@
         <v>82</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D79" t="n">
         <v>1</v>
@@ -6517,7 +6517,7 @@
         <v>84</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81" t="n">
         <v>1</v>
@@ -6750,7 +6750,7 @@
         <v>87</v>
       </c>
       <c r="C84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D84" t="n">
         <v>1</v>
@@ -6821,7 +6821,7 @@
         <v>88</v>
       </c>
       <c r="C85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85" t="n">
         <v>1</v>
@@ -6892,7 +6892,7 @@
         <v>89</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86" t="n">
         <v>1</v>
@@ -7119,7 +7119,7 @@
         <v>92</v>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89" t="n">
         <v>1</v>
@@ -9198,7 +9198,7 @@
         <v>119</v>
       </c>
       <c r="C116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D116" t="n">
         <v>0</v>
@@ -9275,7 +9275,7 @@
         <v>120</v>
       </c>
       <c r="C117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117" t="n">
         <v>0</v>
@@ -9510,7 +9510,7 @@
         <v>123</v>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D120" t="n">
         <v>1</v>
@@ -11208,7 +11208,7 @@
         <v>145</v>
       </c>
       <c r="C142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D142" t="n">
         <v>0</v>
@@ -11753,7 +11753,7 @@
         <v>152</v>
       </c>
       <c r="C149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D149" t="n">
         <v>1</v>
@@ -11828,7 +11828,7 @@
         <v>153</v>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D150" t="n">
         <v>1</v>
@@ -12215,7 +12215,7 @@
         <v>158</v>
       </c>
       <c r="C155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D155" t="n">
         <v>1</v>
@@ -12371,7 +12371,7 @@
         <v>160</v>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D157" t="n">
         <v>1</v>
@@ -12523,7 +12523,7 @@
         <v>162</v>
       </c>
       <c r="C159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D159" t="n">
         <v>1</v>
@@ -13994,7 +13994,7 @@
         <v>181</v>
       </c>
       <c r="C178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D178" t="n">
         <v>1</v>
@@ -14071,7 +14071,7 @@
         <v>182</v>
       </c>
       <c r="C179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D179" t="n">
         <v>0</v>
@@ -14537,7 +14537,7 @@
         <v>188</v>
       </c>
       <c r="C185" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D185" t="n">
         <v>1</v>
@@ -15779,7 +15779,7 @@
         <v>204</v>
       </c>
       <c r="C201" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D201" t="n">
         <v>1</v>
@@ -16241,7 +16241,7 @@
         <v>210</v>
       </c>
       <c r="C207" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D207" t="n">
         <v>1</v>
@@ -17098,7 +17098,7 @@
         <v>221</v>
       </c>
       <c r="C218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D218" t="n">
         <v>1</v>
@@ -17570,7 +17570,7 @@
         <v>227</v>
       </c>
       <c r="C224" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D224" t="n">
         <v>1</v>
@@ -17961,7 +17961,7 @@
         <v>232</v>
       </c>
       <c r="C229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D229" t="n">
         <v>0</v>
@@ -18741,7 +18741,7 @@
         <v>242</v>
       </c>
       <c r="C239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D239" t="n">
         <v>0</v>
@@ -19124,7 +19124,7 @@
         <v>247</v>
       </c>
       <c r="C244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D244" t="n">
         <v>0</v>
@@ -19815,7 +19815,7 @@
         <v>256</v>
       </c>
       <c r="C253" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D253" t="n">
         <v>0</v>
@@ -20121,7 +20121,7 @@
         <v>260</v>
       </c>
       <c r="C257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D257" t="n">
         <v>0</v>
@@ -20747,7 +20747,7 @@
         <v>268</v>
       </c>
       <c r="C265" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D265" t="n">
         <v>1</v>
@@ -21371,7 +21371,7 @@
         <v>276</v>
       </c>
       <c r="C273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D273" t="n">
         <v>0</v>
@@ -21675,7 +21675,7 @@
         <v>281</v>
       </c>
       <c r="C277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D277" t="n">
         <v>0</v>
@@ -22141,7 +22141,7 @@
         <v>287</v>
       </c>
       <c r="C283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D283" t="n">
         <v>0</v>
@@ -24534,7 +24534,7 @@
         <v>318</v>
       </c>
       <c r="C314" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D314" t="n">
         <v>1</v>
@@ -26088,7 +26088,7 @@
         <v>338</v>
       </c>
       <c r="C334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D334" t="n">
         <v>0</v>
@@ -28503,7 +28503,7 @@
         <v>369</v>
       </c>
       <c r="C365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D365" t="n">
         <v>1</v>
@@ -29356,7 +29356,7 @@
         <v>380</v>
       </c>
       <c r="C376" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D376" t="n">
         <v>0</v>
@@ -29905,7 +29905,7 @@
         <v>387</v>
       </c>
       <c r="C383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D383" t="n">
         <v>0</v>
